--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6845866232207336</v>
+        <v>0.6845867017690147</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3383812301963071</v>
+        <v>0.3383810410751992</v>
       </c>
     </row>
     <row r="4">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8041420970692328</v>
+        <v>0.8041420785156048</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.897911633979306</v>
+        <v>0.8979115381258913</v>
       </c>
     </row>
     <row r="6">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7569124375653693</v>
+        <v>0.7569120894492523</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7451864299569575</v>
+        <v>0.7451866231822964</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.760780088963233</v>
+        <v>0.7607798726191958</v>
       </c>
     </row>
     <row r="9">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5903727403635777</v>
+        <v>0.5903726450443131</v>
       </c>
     </row>
     <row r="10">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.69945825627462</v>
+        <v>0.6994580825903529</v>
       </c>
     </row>
   </sheetData>
@@ -723,25 +723,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4626485192674899</v>
+        <v>0.5589844983313628</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4852913081631383</v>
+        <v>0.4852912040259699</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7107163939318962</v>
+        <v>0.7107161905086252</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5589847928813665</v>
+        <v>0.4626482946568332</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4361037461756461</v>
+        <v>0.4361035895025651</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6986764183313601</v>
+        <v>0.6986761338295182</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6845867017690147</v>
+        <v>0.6845896486801267</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3383810410751992</v>
+        <v>0.3383857972536792</v>
       </c>
     </row>
     <row r="4">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8041420785156048</v>
+        <v>0.804145446325978</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8979115381258913</v>
+        <v>0.897913856430492</v>
       </c>
     </row>
     <row r="6">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7569120894492523</v>
+        <v>0.7569124882504117</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7451866231822964</v>
+        <v>0.7451915014857194</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7607798726191958</v>
+        <v>0.7607836960144646</v>
       </c>
     </row>
     <row r="9">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5903726450443131</v>
+        <v>0.5903595893520683</v>
       </c>
     </row>
     <row r="10">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6994580825903529</v>
+        <v>0.6994563835279511</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5589844983313628</v>
+        <v>0.5589872319235494</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4852912040259699</v>
+        <v>0.710714006852612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7107161905086252</v>
+        <v>0.4361005220957239</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4626482946568332</v>
+        <v>0.4626511856295711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -843,25 +843,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4361035895025651</v>
+        <v>0.4852893920007732</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6986761338295182</v>
+        <v>0.6986759429842281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,31 +426,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
@@ -667,6 +679,206 @@
       </c>
       <c r="E10" t="n">
         <v>0.6994563835279511</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-13 19:30:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5805651190349856</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-13 19:30:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.316517790711576</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-13 19:30:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4108504819039644</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-13 19:30:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4876318557186783</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-13 20:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4869721504434713</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4749609064885604</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5306065951377167</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:30:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6524828558750982</v>
       </c>
     </row>
   </sheetData>
@@ -680,36 +892,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
@@ -892,6 +1104,276 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>LA Clippers</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8590492227065436</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7496280754313392</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6468508031883885</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8470377309589494</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2970138311682546</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8596300685545497</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6543681885696864</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6416335152753547</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6312136768470223</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
     </row>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,11 +455,16 @@
           <t>probability_home_win</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>gameId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12 19:00:00</t>
+          <t>2026-03-13 19:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -469,7 +474,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,13 +483,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6845896486801267</v>
+        <v>0.5805651175463636</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22500961</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12 19:00:00</t>
+          <t>2026-03-13 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -494,391 +502,187 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3383857972536792</v>
+        <v>0.3165177947114969</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22500962</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12 19:00:00</t>
+          <t>2026-03-13 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.804145446325978</v>
+        <v>0.4108504845872408</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22500963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12 19:30:00</t>
+          <t>2026-03-13 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.897913856430492</v>
+        <v>0.487631857464644</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22500965</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12 19:30:00</t>
+          <t>2026-03-13 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7569124882504117</v>
+        <v>0.4869721510246243</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22500964</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12 20:00:00</t>
+          <t>2026-03-13 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7451915014857194</v>
+        <v>0.4749609070890131</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22500966</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12 21:00:00</t>
+          <t>2026-03-13 22:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7607836960144646</v>
+        <v>0.5306065948484985</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22500967</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12 21:30:00</t>
+          <t>2026-03-13 22:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5903595893520683</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-12 22:30:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.6994563835279511</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-13 19:30:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.5805651190349856</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-03-13 19:30:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.316517790711576</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-03-13 19:30:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4108504819039644</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-03-13 19:30:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.4876318557186783</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-03-13 20:00:00</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.4869721504434713</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-03-13 22:00:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4749609064885604</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-03-13 22:00:00</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.5306065951377167</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-03-13 22:30:00</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.6524828558750982</v>
+        <v>0.652482854736849</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22500968</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,41 +730,49 @@
           <t>Actual Winner</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gameId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11 00:00:00</t>
+          <t>2026-03-12 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5589872319235494</v>
+        <v>0.6468508019870481</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
-        </is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>22500960</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11 00:00:00</t>
+          <t>2026-03-12 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -970,7 +782,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -979,132 +791,147 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.710714006852612</v>
+        <v>0.8470377267810785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
+      </c>
+      <c r="G3" t="n">
+        <v>22500955</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11 00:00:00</t>
+          <t>2026-03-12 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4361005220957239</v>
+        <v>0.2970138352607768</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
-        </is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>22500954</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11 00:00:00</t>
+          <t>2026-03-12 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4626511856295711</v>
+        <v>0.8596300648781309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
-        </is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>22500956</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11 00:00:00</t>
+          <t>2026-03-12 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4852893920007732</v>
+        <v>0.654368185331398</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
-        </is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>22500953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11 00:00:00</t>
+          <t>2026-03-12 00:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6986759429842281</v>
+        <v>0.6416335120899616</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
-        </is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>22501111</v>
       </c>
     </row>
     <row r="8">
@@ -1129,12 +956,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8590492227065436</v>
+        <v>0.8590492191605033</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
+      </c>
+      <c r="G8" t="n">
+        <v>22500957</v>
       </c>
     </row>
     <row r="9">
@@ -1159,12 +989,15 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7496280754313392</v>
+        <v>0.749628072689052</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
+      </c>
+      <c r="G9" t="n">
+        <v>22500958</v>
       </c>
     </row>
     <row r="10">
@@ -1175,206 +1008,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6468508031883885</v>
+        <v>0.6312136769140898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8470377309589494</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2970138311682546</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.8596300685545497</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.6543681885696864</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.6416335152753547</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.6312136768470223</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
+      <c r="G10" t="n">
+        <v>22500959</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,225 +464,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13 19:30:00</t>
+          <t>2026-03-14 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5805651175463636</v>
+        <v>0.5139601956006994</v>
       </c>
       <c r="F2" t="n">
-        <v>22500961</v>
+        <v>22500969</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13 19:30:00</t>
+          <t>2026-03-14 15:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3165177947114969</v>
+        <v>0.8807083413495183</v>
       </c>
       <c r="F3" t="n">
-        <v>22500962</v>
+        <v>22500970</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13 19:30:00</t>
+          <t>2026-03-14 15:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4108504845872408</v>
+        <v>0.7136236965027833</v>
       </c>
       <c r="F4" t="n">
-        <v>22500963</v>
+        <v>22500973</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13 19:30:00</t>
+          <t>2026-03-14 18:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.487631857464644</v>
+        <v>0.7536711910840024</v>
       </c>
       <c r="F5" t="n">
-        <v>22500965</v>
+        <v>22500971</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13 20:00:00</t>
+          <t>2026-03-14 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4869721510246243</v>
+        <v>0.7101472240243399</v>
       </c>
       <c r="F6" t="n">
-        <v>22500964</v>
+        <v>22500972</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13 22:00:00</t>
+          <t>2026-03-14 20:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4749609070890131</v>
+        <v>0.6421225486059187</v>
       </c>
       <c r="F7" t="n">
-        <v>22500966</v>
+        <v>22500974</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13 22:00:00</t>
+          <t>2026-03-14 22:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5306065948484985</v>
+        <v>0.7866492358616535</v>
       </c>
       <c r="F8" t="n">
-        <v>22500967</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-13 22:30:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.652482854736849</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22500968</v>
+        <v>22500975</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,12 +711,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -754,124 +726,124 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6468508019870481</v>
+        <v>0.730219433274207</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22500960</v>
+        <v>22500968</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8470377267810785</v>
+        <v>0.5861016864721887</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22500955</v>
+        <v>22500966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2970138352607768</v>
+        <v>0.4188486482337365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22500954</v>
+        <v>22500965</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8596300648781309</v>
+        <v>0.3162462892533334</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22500956</v>
+        <v>22500962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -881,7 +853,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -890,7 +862,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.654368185331398</v>
+        <v>0.695789951599302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -898,139 +870,106 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22500953</v>
+        <v>22500961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6416335120899616</v>
+        <v>0.4189104333098274</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22501111</v>
+        <v>22500963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8590492191605033</v>
+        <v>0.3942169236533269</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500957</v>
+        <v>22500964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12 00:00:00</t>
+          <t>2026-03-13 00:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.749628072689052</v>
+        <v>0.5696450348251237</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>22500958</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.6312136769140898</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>22500959</v>
+        <v>22500967</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -464,197 +464,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-14 13:00:00</t>
+          <t>2026-03-15 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5139601956006994</v>
+        <v>0.7964743971824646</v>
       </c>
       <c r="F2" t="n">
-        <v>22500969</v>
+        <v>22500976</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-14 15:00:00</t>
+          <t>2026-03-15 15:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8807083413495183</v>
+        <v>0.7323212623596191</v>
       </c>
       <c r="F3" t="n">
-        <v>22500970</v>
+        <v>22500977</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-14 15:30:00</t>
+          <t>2026-03-15 15:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7136236965027833</v>
+        <v>0.5554024577140808</v>
       </c>
       <c r="F4" t="n">
-        <v>22500973</v>
+        <v>22500978</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-14 18:00:00</t>
+          <t>2026-03-15 15:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7536711910840024</v>
+        <v>0.7607907652854919</v>
       </c>
       <c r="F5" t="n">
-        <v>22500971</v>
+        <v>22500979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-14 20:00:00</t>
+          <t>2026-03-15 18:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7101472240243399</v>
+        <v>0.5696443915367126</v>
       </c>
       <c r="F6" t="n">
-        <v>22500972</v>
+        <v>22500980</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-14 20:30:00</t>
+          <t>2026-03-15 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6421225486059187</v>
+        <v>0.5972367525100708</v>
       </c>
       <c r="F7" t="n">
-        <v>22500974</v>
+        <v>22500981</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-14 22:30:00</t>
+          <t>2026-03-15 22:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
       <c r="E8" t="n">
-        <v>0.7866492358616535</v>
+        <v>0.5211443901062012</v>
       </c>
       <c r="F8" t="n">
-        <v>22500975</v>
+        <v>22500982</v>
       </c>
     </row>
   </sheetData>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,265 +711,232 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.730219433274207</v>
+        <v>0.8429240584373474</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22500968</v>
+        <v>22500970</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5861016864721887</v>
+        <v>0.6524375677108765</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22500966</v>
+        <v>22500973</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4188486482337365</v>
+        <v>0.8574886322021484</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22500965</v>
+        <v>22500971</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3162462892533334</v>
+        <v>0.4993022978305817</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22500962</v>
+        <v>22500972</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.695789951599302</v>
+        <v>0.6525467038154602</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22500961</v>
+        <v>22500974</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4189104333098274</v>
+        <v>0.5775021314620972</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22500963</v>
+        <v>22500969</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13 00:00:00</t>
+          <t>2026-03-14 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3942169236533269</v>
+        <v>0.5777215957641602</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500964</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.5696450348251237</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>22500967</v>
+        <v>22500975</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,36 +414,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -464,68 +452,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-15 13:00:00</t>
+          <t>2026-03-17 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7964743971824646</v>
+        <v>0.6810544729232788</v>
       </c>
       <c r="F2" t="n">
-        <v>22500976</v>
+        <v>22500991</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-15 15:30:00</t>
+          <t>2026-03-17 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7323212623596191</v>
+        <v>0.5519959330558777</v>
       </c>
       <c r="F3" t="n">
-        <v>22500977</v>
+        <v>22500992</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-15 15:30:00</t>
+          <t>2026-03-17 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -535,25 +523,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5554024577140808</v>
+        <v>0.1888937950134277</v>
       </c>
       <c r="F4" t="n">
-        <v>22500978</v>
+        <v>22500993</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-15 15:30:00</t>
+          <t>2026-03-17 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,98 +551,126 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7607907652854919</v>
+        <v>0.7929907441139221</v>
       </c>
       <c r="F5" t="n">
-        <v>22500979</v>
+        <v>22500994</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-15 18:00:00</t>
+          <t>2026-03-17 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5696443915367126</v>
+        <v>0.283492237329483</v>
       </c>
       <c r="F6" t="n">
-        <v>22500980</v>
+        <v>22500995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-15 20:00:00</t>
+          <t>2026-03-17 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5972367525100708</v>
+        <v>0.6228559017181396</v>
       </c>
       <c r="F7" t="n">
-        <v>22500981</v>
+        <v>22500996</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-15 22:00:00</t>
+          <t>2026-03-17 22:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6973309516906738</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22500997</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.5211443901062012</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22500982</v>
+      <c r="E9" t="n">
+        <v>0.585138201713562</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22500998</v>
       </c>
     </row>
   </sheetData>
@@ -668,41 +684,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -711,232 +727,265 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8429240584373474</v>
+        <v>0.7718399167060852</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22500970</v>
+        <v>22500988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6524375677108765</v>
+        <v>0.6628966331481934</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22500973</v>
+        <v>22500986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8574886322021484</v>
+        <v>0.222200021147728</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22500971</v>
+        <v>22500984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4993022978305817</v>
+        <v>0.4305817782878876</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22500972</v>
+        <v>22500989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6525467038154602</v>
+        <v>0.5851534008979797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22500974</v>
+        <v>22500990</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5775021314620972</v>
+        <v>0.5979579091072083</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22500969</v>
+        <v>22500983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-14 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5777215957641602</v>
+        <v>0.5038461685180664</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500975</v>
+        <v>22500985</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6791099905967712</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>22500987</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -467,11 +467,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6810544729232788</v>
+        <v>0.4883840680122375</v>
       </c>
       <c r="F2" t="n">
         <v>22500991</v>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5519959330558777</v>
+        <v>0.5127621293067932</v>
       </c>
       <c r="F3" t="n">
         <v>22500992</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1888937950134277</v>
+        <v>0.2308535128831863</v>
       </c>
       <c r="F4" t="n">
         <v>22500993</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7929907441139221</v>
+        <v>0.8522992730140686</v>
       </c>
       <c r="F5" t="n">
         <v>22500994</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.283492237329483</v>
+        <v>0.2684666216373444</v>
       </c>
       <c r="F6" t="n">
         <v>22500995</v>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6228559017181396</v>
+        <v>0.6778576970100403</v>
       </c>
       <c r="F7" t="n">
         <v>22500996</v>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6973309516906738</v>
+        <v>0.6111695766448975</v>
       </c>
       <c r="F8" t="n">
         <v>22500997</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.585138201713562</v>
+        <v>0.5191518068313599</v>
       </c>
       <c r="F9" t="n">
         <v>22500998</v>
@@ -732,29 +732,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7718399167060852</v>
+        <v>0.3228119611740112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22500988</v>
+        <v>22500989</v>
       </c>
     </row>
     <row r="3">
@@ -765,29 +765,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6628966331481934</v>
+        <v>0.4246545135974884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22500986</v>
+        <v>22500990</v>
       </c>
     </row>
     <row r="4">
@@ -798,29 +798,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.222200021147728</v>
+        <v>0.628429651260376</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22500984</v>
+        <v>22500983</v>
       </c>
     </row>
     <row r="5">
@@ -831,29 +831,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4305817782878876</v>
+        <v>0.2950863242149353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22500989</v>
+        <v>22500985</v>
       </c>
     </row>
     <row r="6">
@@ -864,29 +864,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5851534008979797</v>
+        <v>0.8141456246376038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22500990</v>
+        <v>22500988</v>
       </c>
     </row>
     <row r="7">
@@ -897,29 +897,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5979579091072083</v>
+        <v>0.7310704588890076</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22500983</v>
+        <v>22500986</v>
       </c>
     </row>
     <row r="8">
@@ -930,29 +930,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5038461685180664</v>
+        <v>0.1696883141994476</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500985</v>
+        <v>22500984</v>
       </c>
     </row>
     <row r="9">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6791099905967712</v>
+        <v>0.7086217999458313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,40 +452,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17 19:00:00</t>
+          <t>2026-03-18 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4883840680122375</v>
+        <v>0.7046881318092346</v>
       </c>
       <c r="F2" t="n">
-        <v>22500991</v>
+        <v>22500999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17 19:00:00</t>
+          <t>2026-03-18 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,182 +495,210 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5127621293067932</v>
+        <v>0.3010091483592987</v>
       </c>
       <c r="F3" t="n">
-        <v>22500992</v>
+        <v>22501000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17 19:00:00</t>
+          <t>2026-03-18 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2308535128831863</v>
+        <v>0.2131834179162979</v>
       </c>
       <c r="F4" t="n">
-        <v>22500993</v>
+        <v>22501001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17 19:30:00</t>
+          <t>2026-03-18 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8522992730140686</v>
+        <v>0.6208163499832153</v>
       </c>
       <c r="F5" t="n">
-        <v>22500994</v>
+        <v>22501002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17 20:00:00</t>
+          <t>2026-03-18 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2684666216373444</v>
+        <v>0.6639977693557739</v>
       </c>
       <c r="F6" t="n">
-        <v>22500995</v>
+        <v>22501004</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17 20:00:00</t>
+          <t>2026-03-18 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6778576970100403</v>
+        <v>0.6190536022186279</v>
       </c>
       <c r="F7" t="n">
-        <v>22500996</v>
+        <v>22501005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17 22:00:00</t>
+          <t>2026-03-18 20:30:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6111695766448975</v>
+        <v>0.5686780214309692</v>
       </c>
       <c r="F8" t="n">
-        <v>22500997</v>
+        <v>22500651</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17 22:00:00</t>
+          <t>2026-03-18 20:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5191518068313599</v>
+        <v>0.1298697739839554</v>
       </c>
       <c r="F9" t="n">
-        <v>22500998</v>
+        <v>22501006</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-18 21:30:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3476361036300659</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501007</v>
       </c>
     </row>
   </sheetData>
@@ -727,265 +755,265 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3228119611740112</v>
+        <v>0.4343498349189758</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22500989</v>
+        <v>22500996</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4246545135974884</v>
+        <v>0.3743271231651306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22500990</v>
+        <v>22500995</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.628429651260376</v>
+        <v>0.2116377651691437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22500983</v>
+        <v>22500992</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2950863242149353</v>
+        <v>0.7550305724143982</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22500985</v>
+        <v>22500994</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8141456246376038</v>
+        <v>0.5457360744476318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22500988</v>
+        <v>22500991</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7310704588890076</v>
+        <v>0.1621145457029343</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22500986</v>
+        <v>22500993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.1696883141994476</v>
+        <v>0.3026701211929321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500984</v>
+        <v>22500998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7086217999458313</v>
+        <v>0.6574461460113525</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>22500987</v>
+        <v>22500997</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7046881318092346</v>
+        <v>0.7294707894325256</v>
       </c>
       <c r="F2" t="n">
         <v>22500999</v>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3010091483592987</v>
+        <v>0.2842900454998016</v>
       </c>
       <c r="F3" t="n">
         <v>22501000</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2131834179162979</v>
+        <v>0.2439689189195633</v>
       </c>
       <c r="F4" t="n">
         <v>22501001</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6208163499832153</v>
+        <v>0.5209299325942993</v>
       </c>
       <c r="F5" t="n">
         <v>22501002</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6639977693557739</v>
+        <v>0.6554064154624939</v>
       </c>
       <c r="F6" t="n">
         <v>22501004</v>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6190536022186279</v>
+        <v>0.5324534177780151</v>
       </c>
       <c r="F7" t="n">
         <v>22501005</v>
@@ -635,11 +635,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5686780214309692</v>
+        <v>0.494267612695694</v>
       </c>
       <c r="F8" t="n">
         <v>22500651</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1298697739839554</v>
+        <v>0.1570685207843781</v>
       </c>
       <c r="F9" t="n">
         <v>22501006</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3476361036300659</v>
+        <v>0.3276689648628235</v>
       </c>
       <c r="F10" t="n">
         <v>22501007</v>
@@ -760,29 +760,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4343498349189758</v>
+        <v>0.2662922739982605</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22500996</v>
+        <v>22500995</v>
       </c>
     </row>
     <row r="3">
@@ -793,29 +793,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3743271231651306</v>
+        <v>0.5137976408004761</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22500995</v>
+        <v>22500996</v>
       </c>
     </row>
     <row r="4">
@@ -826,29 +826,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2116377651691437</v>
+        <v>0.3884319663047791</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22500992</v>
+        <v>22500998</v>
       </c>
     </row>
     <row r="5">
@@ -859,29 +859,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7550305724143982</v>
+        <v>0.2785426378250122</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22500994</v>
+        <v>22500992</v>
       </c>
     </row>
     <row r="6">
@@ -892,29 +892,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5457360744476318</v>
+        <v>0.1558626741170883</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22500991</v>
+        <v>22500993</v>
       </c>
     </row>
     <row r="7">
@@ -925,29 +925,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1621145457029343</v>
+        <v>0.5540216565132141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22500993</v>
+        <v>22500991</v>
       </c>
     </row>
     <row r="8">
@@ -958,29 +958,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3026701211929321</v>
+        <v>0.8187637329101562</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500998</v>
+        <v>22500994</v>
       </c>
     </row>
     <row r="9">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6574461460113525</v>
+        <v>0.6405219435691833</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="predictions_today" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yesterday" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,36 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -452,91 +463,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:00</t>
+          <t>2026-03-19 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7294707894325256</v>
+        <v>0.5466242432594299</v>
       </c>
       <c r="F2" t="n">
-        <v>22500999</v>
+        <v>22501008</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18 19:30:00</t>
+          <t>2026-03-19 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2842900454998016</v>
+        <v>0.156985729932785</v>
       </c>
       <c r="F3" t="n">
-        <v>22501000</v>
+        <v>22501009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18 19:30:00</t>
+          <t>2026-03-19 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2439689189195633</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F4" t="n">
-        <v>22501001</v>
+        <v>22501010</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18 20:00:00</t>
+          <t>2026-03-19 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,474 +557,131 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5209299325942993</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F5" t="n">
-        <v>22501002</v>
+        <v>22501011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18 20:00:00</t>
+          <t>2026-03-19 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6554064154624939</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F6" t="n">
-        <v>22501004</v>
+        <v>22501012</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18 20:00:00</t>
+          <t>2026-03-19 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5324534177780151</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F7" t="n">
-        <v>22501005</v>
+        <v>22501013</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18 20:30:00</t>
+          <t>2026-03-19 21:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.494267612695694</v>
+        <v>0.5481546521186829</v>
       </c>
       <c r="F8" t="n">
-        <v>22500651</v>
+        <v>22501014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18 20:30:00</t>
+          <t>2026-03-19 22:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1570685207843781</v>
+        <v>0.7287593483924866</v>
       </c>
       <c r="F9" t="n">
-        <v>22501006</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-18 21:30:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3276689648628235</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501007</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Home Team</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Away Team</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Predicted Winner</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>probability_home_win</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Actual Winner</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>gameId</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.2662922739982605</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>22500995</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.5137976408004761</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>22500996</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3884319663047791</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>22500998</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.2785426378250122</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>22500992</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1558626741170883</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>22500993</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5540216565132141</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>22500991</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.8187637329101562</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>22500994</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6405219435691833</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>22500997</v>
+        <v>22501015</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,68 +463,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19 19:00:00</t>
+          <t>2026-03-21 17:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5466242432594299</v>
+        <v>0.3804706037044525</v>
       </c>
       <c r="F2" t="n">
-        <v>22501008</v>
+        <v>22501022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19 19:00:00</t>
+          <t>2026-03-21 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.156985729932785</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F3" t="n">
-        <v>22501009</v>
+        <v>22501023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19 20:00:00</t>
+          <t>2026-03-21 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -534,25 +534,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.499740868806839</v>
+        <v>0.5733375549316406</v>
       </c>
       <c r="F4" t="n">
-        <v>22501010</v>
+        <v>22501024</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19 20:00:00</t>
+          <t>2026-03-21 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,122 +566,178 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.462356299161911</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F5" t="n">
-        <v>22501011</v>
+        <v>22501025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19 20:00:00</t>
+          <t>2026-03-21 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F6" t="n">
-        <v>22501012</v>
+        <v>22501026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19 20:00:00</t>
+          <t>2026-03-21 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.4926076531410217</v>
       </c>
       <c r="F7" t="n">
-        <v>22501013</v>
+        <v>22501027</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-19 21:00:00</t>
+          <t>2026-03-21 20:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5481546521186829</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F8" t="n">
-        <v>22501014</v>
+        <v>22501028</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-19 22:00:00</t>
+          <t>2026-03-21 20:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4836676120758057</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501029</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-21 21:30:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.7287593483924866</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501015</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.443777859210968</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501030</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7414435744285583</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22501031</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -463,281 +451,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-21 17:00:00</t>
+          <t>2026-03-22 17:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3804706037044525</v>
+        <v>0.6782870292663574</v>
       </c>
       <c r="F2" t="n">
-        <v>22501022</v>
+        <v>22501032</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-21 19:00:00</t>
+          <t>2026-03-22 18:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.6460906267166138</v>
       </c>
       <c r="F3" t="n">
-        <v>22501023</v>
+        <v>22501033</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-21 19:00:00</t>
+          <t>2026-03-22 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5733375549316406</v>
+        <v>0.8850165605545044</v>
       </c>
       <c r="F4" t="n">
-        <v>22501024</v>
+        <v>22501034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-21 19:00:00</t>
+          <t>2026-03-22 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.7512719631195068</v>
       </c>
       <c r="F5" t="n">
-        <v>22501025</v>
+        <v>22501035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-21 20:00:00</t>
+          <t>2026-03-22 21:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.5605062246322632</v>
       </c>
       <c r="F6" t="n">
-        <v>22501026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-21 20:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.4926076531410217</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22501027</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-21 20:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.8616619110107422</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501028</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-21 20:30:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.4836676120758057</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501029</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-21 21:30:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.443777859210968</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501030</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-21 22:00:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.7414435744285583</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22501031</v>
+        <v>22501036</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,141 +451,281 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-22 17:00:00</t>
+          <t>2026-03-23 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6782870292663574</v>
+        <v>0.6078159809112549</v>
       </c>
       <c r="F2" t="n">
-        <v>22501032</v>
+        <v>22501038</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-22 18:00:00</t>
+          <t>2026-03-23 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6460906267166138</v>
+        <v>0.7137834429740906</v>
       </c>
       <c r="F3" t="n">
-        <v>22501033</v>
+        <v>22501039</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-22 19:30:00</t>
+          <t>2026-03-23 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8850165605545044</v>
+        <v>0.2557961344718933</v>
       </c>
       <c r="F4" t="n">
-        <v>22501034</v>
+        <v>22501040</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-22 20:00:00</t>
+          <t>2026-03-23 19:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7512719631195068</v>
+        <v>0.5200976729393005</v>
       </c>
       <c r="F5" t="n">
-        <v>22501035</v>
+        <v>22501041</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-22 21:00:00</t>
+          <t>2026-03-23 19:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8431744575500488</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22501037</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-23 20:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5208929777145386</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22501042</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-23 21:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.5605062246322632</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22501036</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3560488522052765</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22501043</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-23 21:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6753662824630737</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501044</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7495328187942505</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501045</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:30:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7013514041900635</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22501046</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,36 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -451,281 +463,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23 19:00:00</t>
+          <t>2026-03-24 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6078159809112549</v>
+        <v>0.7356671094894409</v>
       </c>
       <c r="F2" t="n">
-        <v>22501038</v>
+        <v>22501047</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23 19:00:00</t>
+          <t>2026-03-24 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7137834429740906</v>
+        <v>0.7157652378082275</v>
       </c>
       <c r="F3" t="n">
-        <v>22501039</v>
+        <v>22501048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23 19:00:00</t>
+          <t>2026-03-24 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2557961344718933</v>
+        <v>0.7073813676834106</v>
       </c>
       <c r="F4" t="n">
-        <v>22501040</v>
+        <v>22501049</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23 19:00:00</t>
+          <t>2026-03-24 23:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5200976729393005</v>
+        <v>0.4800166189670563</v>
       </c>
       <c r="F5" t="n">
-        <v>22501041</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-23 19:30:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8431744575500488</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22501037</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-23 20:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5208929777145386</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22501042</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-23 21:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3560488522052765</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501043</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-23 21:30:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6753662824630737</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501044</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-23 22:00:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.7495328187942505</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501045</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-23 22:30:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.7013514041900635</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22501046</v>
+        <v>22501050</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -463,113 +451,337 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24 19:00:00</t>
+          <t>2026-03-25 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7356671094894409</v>
+        <v>0.5882400870323181</v>
       </c>
       <c r="F2" t="n">
-        <v>22501047</v>
+        <v>22501051</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24 19:30:00</t>
+          <t>2026-03-25 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7157652378082275</v>
+        <v>0.3540230095386505</v>
       </c>
       <c r="F3" t="n">
-        <v>22501048</v>
+        <v>22501052</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24 20:00:00</t>
+          <t>2026-03-25 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7073813676834106</v>
+        <v>0.7345883250236511</v>
       </c>
       <c r="F4" t="n">
-        <v>22501049</v>
+        <v>22501053</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24 23:00:00</t>
+          <t>2026-03-25 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5735021829605103</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22501054</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:30:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6663347482681274</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22501055</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3558185696601868</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22501056</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-25 21:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7327764630317688</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22501057</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-25 21:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7012732028961182</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501058</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-25 22:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.4800166189670563</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22501050</v>
+      <c r="E10" t="n">
+        <v>0.7136558294296265</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501059</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-25 22:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8636989593505859</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22501060</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-25 22:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6992468237876892</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22501061</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-25 22:30:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4335979521274567</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22501062</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,236 +451,236 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25 19:00:00</t>
+          <t>2026-03-27 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5882400870323181</v>
+        <v>0.3163451850414276</v>
       </c>
       <c r="F2" t="n">
-        <v>22501051</v>
+        <v>22501066</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25 19:00:00</t>
+          <t>2026-03-27 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3540230095386505</v>
+        <v>0.6011347770690918</v>
       </c>
       <c r="F3" t="n">
-        <v>22501052</v>
+        <v>22501067</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25 19:00:00</t>
+          <t>2026-03-27 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7345883250236511</v>
+        <v>0.7299258708953857</v>
       </c>
       <c r="F4" t="n">
-        <v>22501053</v>
+        <v>22501068</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25 19:30:00</t>
+          <t>2026-03-27 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5735021829605103</v>
+        <v>0.3269562125205994</v>
       </c>
       <c r="F5" t="n">
-        <v>22501054</v>
+        <v>22501069</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25 19:30:00</t>
+          <t>2026-03-27 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6663347482681274</v>
+        <v>0.8295520544052124</v>
       </c>
       <c r="F6" t="n">
-        <v>22501055</v>
+        <v>22501070</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25 20:00:00</t>
+          <t>2026-03-27 20:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3558185696601868</v>
+        <v>0.6670945882797241</v>
       </c>
       <c r="F7" t="n">
-        <v>22501056</v>
+        <v>22501071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25 21:00:00</t>
+          <t>2026-03-27 21:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7327764630317688</v>
+        <v>0.8279622793197632</v>
       </c>
       <c r="F8" t="n">
-        <v>22501057</v>
+        <v>22501072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25 21:30:00</t>
+          <t>2026-03-27 22:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7012732028961182</v>
+        <v>0.7257824540138245</v>
       </c>
       <c r="F9" t="n">
-        <v>22501058</v>
+        <v>22501073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25 22:00:00</t>
+          <t>2026-03-27 22:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -690,25 +690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7136558294296265</v>
+        <v>0.7883844375610352</v>
       </c>
       <c r="F10" t="n">
-        <v>22501059</v>
+        <v>22501074</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25 22:00:00</t>
+          <t>2026-03-27 22:30:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -718,70 +718,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8636989593505859</v>
+        <v>0.8457854390144348</v>
       </c>
       <c r="F11" t="n">
-        <v>22501060</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-03-25 22:00:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6992468237876892</v>
-      </c>
-      <c r="F12" t="n">
-        <v>22501061</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-03-25 22:30:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4335979521274567</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22501062</v>
+        <v>22501075</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,124 +451,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27 19:00:00</t>
+          <t>2026-03-28 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3163451850414276</v>
+        <v>0.3542602062225342</v>
       </c>
       <c r="F2" t="n">
-        <v>22501066</v>
+        <v>22501076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27 19:30:00</t>
+          <t>2026-03-28 17:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6011347770690918</v>
+        <v>0.4755303859710693</v>
       </c>
       <c r="F3" t="n">
-        <v>22501067</v>
+        <v>22501080</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27 19:30:00</t>
+          <t>2026-03-28 18:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7299258708953857</v>
+        <v>0.6064226627349854</v>
       </c>
       <c r="F4" t="n">
-        <v>22501068</v>
+        <v>22501077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27 20:00:00</t>
+          <t>2026-03-28 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3269562125205994</v>
+        <v>0.7755086421966553</v>
       </c>
       <c r="F5" t="n">
-        <v>22501069</v>
+        <v>22501078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27 20:00:00</t>
+          <t>2026-03-28 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,154 +578,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8295520544052124</v>
+        <v>0.3101013600826263</v>
       </c>
       <c r="F6" t="n">
-        <v>22501070</v>
+        <v>22501079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27 20:30:00</t>
+          <t>2026-03-28 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6670945882797241</v>
+        <v>0.8269034624099731</v>
       </c>
       <c r="F7" t="n">
-        <v>22501071</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-27 21:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.8279622793197632</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501072</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-27 22:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.7257824540138245</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501073</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-27 22:00:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.7883844375610352</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501074</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-27 22:30:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8457854390144348</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22501075</v>
+        <v>22501081</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,169 +451,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28 15:00:00</t>
+          <t>2026-03-30 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3542602062225342</v>
+        <v>0.4759908616542816</v>
       </c>
       <c r="F2" t="n">
-        <v>22501076</v>
+        <v>22501091</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28 17:30:00</t>
+          <t>2026-03-30 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4755303859710693</v>
+        <v>0.3622306883335114</v>
       </c>
       <c r="F3" t="n">
-        <v>22501080</v>
+        <v>22501092</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-28 18:00:00</t>
+          <t>2026-03-30 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6064226627349854</v>
+        <v>0.1846820116043091</v>
       </c>
       <c r="F4" t="n">
-        <v>22501077</v>
+        <v>22501093</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28 19:30:00</t>
+          <t>2026-03-30 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7755086421966553</v>
+        <v>0.7859463095664978</v>
       </c>
       <c r="F5" t="n">
-        <v>22501078</v>
+        <v>22501094</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-28 20:00:00</t>
+          <t>2026-03-30 20:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3101013600826263</v>
+        <v>0.2331387102603912</v>
       </c>
       <c r="F6" t="n">
-        <v>22501079</v>
+        <v>22501095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-28 22:00:00</t>
+          <t>2026-03-30 21:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8269034624099731</v>
+        <v>0.3524667322635651</v>
       </c>
       <c r="F7" t="n">
-        <v>22501081</v>
+        <v>22501096</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:30:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.607979416847229</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22501097</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7356448173522949</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501098</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,152 +451,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30 19:00:00</t>
+          <t>2026-03-31 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4759908616542816</v>
+        <v>0.4455626606941223</v>
       </c>
       <c r="F2" t="n">
-        <v>22501091</v>
+        <v>22501099</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30 19:30:00</t>
+          <t>2026-03-31 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3622306883335114</v>
+        <v>0.3104596138000488</v>
       </c>
       <c r="F3" t="n">
-        <v>22501092</v>
+        <v>22501100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30 20:00:00</t>
+          <t>2026-03-31 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1846820116043091</v>
+        <v>0.5768108367919922</v>
       </c>
       <c r="F4" t="n">
-        <v>22501093</v>
+        <v>22500652</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30 20:00:00</t>
+          <t>2026-03-31 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7859463095664978</v>
+        <v>0.629755437374115</v>
       </c>
       <c r="F5" t="n">
-        <v>22501094</v>
+        <v>22501101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30 20:30:00</t>
+          <t>2026-03-31 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2331387102603912</v>
+        <v>0.3904860615730286</v>
       </c>
       <c r="F6" t="n">
-        <v>22501095</v>
+        <v>22501102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30 21:00:00</t>
+          <t>2026-03-31 22:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -606,70 +606,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3524667322635651</v>
+        <v>0.6365575194358826</v>
       </c>
       <c r="F7" t="n">
-        <v>22501096</v>
+        <v>22501103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30 21:30:00</t>
+          <t>2026-03-31 23:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.607979416847229</v>
+        <v>0.5477316975593567</v>
       </c>
       <c r="F8" t="n">
-        <v>22501097</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-30 22:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.7356448173522949</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501098</v>
+        <v>22501104</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,197 +451,253 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31 19:00:00</t>
+          <t>2026-04-01 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4455626606941223</v>
+        <v>0.3167918026447296</v>
       </c>
       <c r="F2" t="n">
-        <v>22501099</v>
+        <v>22501105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31 19:30:00</t>
+          <t>2026-04-01 19:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3104596138000488</v>
+        <v>0.4533692002296448</v>
       </c>
       <c r="F3" t="n">
-        <v>22501100</v>
+        <v>22501106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31 20:00:00</t>
+          <t>2026-04-01 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5768108367919922</v>
+        <v>0.3006761372089386</v>
       </c>
       <c r="F4" t="n">
-        <v>22500652</v>
+        <v>22501107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31 20:00:00</t>
+          <t>2026-04-01 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.629755437374115</v>
+        <v>0.334742397069931</v>
       </c>
       <c r="F5" t="n">
-        <v>22501101</v>
+        <v>22501003</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31 20:00:00</t>
+          <t>2026-04-01 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3904860615730286</v>
+        <v>0.7200018763542175</v>
       </c>
       <c r="F6" t="n">
-        <v>22501102</v>
+        <v>22501108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31 22:30:00</t>
+          <t>2026-04-01 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6365575194358826</v>
+        <v>0.6811369657516479</v>
       </c>
       <c r="F7" t="n">
-        <v>22501103</v>
+        <v>22501109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31 23:00:00</t>
+          <t>2026-04-01 20:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5477316975593567</v>
+        <v>0.7958841919898987</v>
       </c>
       <c r="F8" t="n">
-        <v>22501104</v>
+        <v>22501110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3026004433631897</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501112</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3299661874771118</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501113</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -451,68 +451,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01 19:00:00</t>
+          <t>2026-04-03 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3167918026447296</v>
+        <v>0.7051196098327637</v>
       </c>
       <c r="F2" t="n">
-        <v>22501105</v>
+        <v>22501120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01 19:30:00</t>
+          <t>2026-04-03 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4533692002296448</v>
+        <v>0.5093315839767456</v>
       </c>
       <c r="F3" t="n">
-        <v>22501106</v>
+        <v>22501121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01 19:30:00</t>
+          <t>2026-04-03 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -526,178 +526,178 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3006761372089386</v>
+        <v>0.313143253326416</v>
       </c>
       <c r="F4" t="n">
-        <v>22501107</v>
+        <v>22501122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01 20:00:00</t>
+          <t>2026-04-03 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
       <c r="E5" t="n">
-        <v>0.334742397069931</v>
+        <v>0.869844377040863</v>
       </c>
       <c r="F5" t="n">
-        <v>22501003</v>
+        <v>22501123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01 20:00:00</t>
+          <t>2026-04-03 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7200018763542175</v>
+        <v>0.8550282120704651</v>
       </c>
       <c r="F6" t="n">
-        <v>22501108</v>
+        <v>22501124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01 20:00:00</t>
+          <t>2026-04-03 20:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6811369657516479</v>
+        <v>0.236572340130806</v>
       </c>
       <c r="F7" t="n">
-        <v>22501109</v>
+        <v>22501125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01 20:00:00</t>
+          <t>2026-04-03 20:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7958841919898987</v>
+        <v>0.3213936686515808</v>
       </c>
       <c r="F8" t="n">
-        <v>22501110</v>
+        <v>22501126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01 21:00:00</t>
+          <t>2026-04-03 20:30:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3026004433631897</v>
+        <v>0.4103548228740692</v>
       </c>
       <c r="F9" t="n">
-        <v>22501112</v>
+        <v>22501127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01 22:00:00</t>
+          <t>2026-04-03 22:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3299661874771118</v>
+        <v>0.7199352979660034</v>
       </c>
       <c r="F10" t="n">
-        <v>22501113</v>
+        <v>22501128</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,36 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -451,253 +463,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03 19:00:00</t>
+          <t>2026-04-04 15:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7051196098327637</v>
+        <v>0.6822111010551453</v>
       </c>
       <c r="F2" t="n">
-        <v>22501120</v>
+        <v>22501129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03 19:00:00</t>
+          <t>2026-04-04 15:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5093315839767456</v>
+        <v>0.6619012355804443</v>
       </c>
       <c r="F3" t="n">
-        <v>22501121</v>
+        <v>22501130</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03 19:30:00</t>
+          <t>2026-04-04 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.313143253326416</v>
+        <v>0.5364096760749817</v>
       </c>
       <c r="F4" t="n">
-        <v>22501122</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-03 19:30:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.869844377040863</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22501123</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-03 20:00:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8550282120704651</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22501124</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-03 20:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.236572340130806</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22501125</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-03 20:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3213936686515808</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501126</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-03 20:30:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.4103548228740692</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501127</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-04-03 22:00:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.7199352979660034</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501128</v>
+        <v>22501131</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,85 +463,309 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:00:00</t>
+          <t>2026-04-05 15:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6822111010551453</v>
+        <v>0.6894626617431641</v>
       </c>
       <c r="F2" t="n">
-        <v>22501129</v>
+        <v>22501132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04 15:00:00</t>
+          <t>2026-04-05 15:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6619012355804443</v>
+        <v>0.4391545355319977</v>
       </c>
       <c r="F3" t="n">
-        <v>22501130</v>
+        <v>22501133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04 19:00:00</t>
+          <t>2026-04-05 15:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5364096760749817</v>
+        <v>0.209761306643486</v>
       </c>
       <c r="F4" t="n">
-        <v>22501131</v>
+        <v>22501134</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:30:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6839718818664551</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22501135</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-05 18:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5989465713500977</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22501136</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6429611444473267</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22501137</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5532301664352417</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22501138</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-05 19:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8973514437675476</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501139</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-05 19:30:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3314782083034515</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501140</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-05 21:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2489812076091766</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22501141</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4032554924488068</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22501142</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,309 +463,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00</t>
+          <t>2026-04-06 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6894626617431641</v>
+        <v>0.5972306132316589</v>
       </c>
       <c r="F2" t="n">
-        <v>22501132</v>
+        <v>22501143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00</t>
+          <t>2026-04-06 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4391545355319977</v>
+        <v>0.2161738723516464</v>
       </c>
       <c r="F3" t="n">
-        <v>22501133</v>
+        <v>22501144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00</t>
+          <t>2026-04-06 20:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.209761306643486</v>
+        <v>0.3576884865760803</v>
       </c>
       <c r="F4" t="n">
-        <v>22501134</v>
+        <v>22501145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00</t>
+          <t>2026-04-06 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6839718818664551</v>
+        <v>0.6878817677497864</v>
       </c>
       <c r="F5" t="n">
-        <v>22501135</v>
+        <v>22501146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-05 18:00:00</t>
+          <t>2026-04-06 21:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5989465713500977</v>
+        <v>0.5550410151481628</v>
       </c>
       <c r="F6" t="n">
-        <v>22501136</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-05 19:00:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.6429611444473267</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22501137</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-05 19:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.5532301664352417</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501138</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-05 19:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8973514437675476</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501139</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-04-05 19:30:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3314782083034515</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501140</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04-05 21:00:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.2489812076091766</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22501141</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-04-05 22:00:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4032554924488068</v>
-      </c>
-      <c r="F12" t="n">
-        <v>22501142</v>
+        <v>22501147</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,35 +463,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06 19:00:00</t>
+          <t>2026-04-08 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5972306132316589</v>
+        <v>0.5356937646865845</v>
       </c>
       <c r="F2" t="n">
-        <v>22501143</v>
+        <v>22501158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-06 19:00:00</t>
+          <t>2026-04-08 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -501,86 +501,86 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2161738723516464</v>
+        <v>0.4664558172225952</v>
       </c>
       <c r="F3" t="n">
-        <v>22501144</v>
+        <v>22501159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-06 20:00:00</t>
+          <t>2026-04-08 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3576884865760803</v>
+        <v>0.6002041697502136</v>
       </c>
       <c r="F4" t="n">
-        <v>22501145</v>
+        <v>22501160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-06 20:00:00</t>
+          <t>2026-04-08 21:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6878817677497864</v>
+        <v>0.8839766979217529</v>
       </c>
       <c r="F5" t="n">
-        <v>22501146</v>
+        <v>22501162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-06 21:00:00</t>
+          <t>2026-04-08 21:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,14 +590,70 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5550410151481628</v>
+        <v>0.5398016571998596</v>
       </c>
       <c r="F6" t="n">
-        <v>22501147</v>
+        <v>22501161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3676699697971344</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22501163</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.73008793592453</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22501164</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -463,197 +451,169 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08 19:00:00</t>
+          <t>2026-04-09 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5356937646865845</v>
+        <v>0.7684751152992249</v>
       </c>
       <c r="F2" t="n">
-        <v>22501158</v>
+        <v>22501165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08 19:00:00</t>
+          <t>2026-04-09 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4664558172225952</v>
+        <v>0.2770043313503265</v>
       </c>
       <c r="F3" t="n">
-        <v>22501159</v>
+        <v>22501166</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08 19:00:00</t>
+          <t>2026-04-09 19:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6002041697502136</v>
+        <v>0.4195958077907562</v>
       </c>
       <c r="F4" t="n">
-        <v>22501160</v>
+        <v>22501167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08 21:00:00</t>
+          <t>2026-04-09 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8839766979217529</v>
+        <v>0.3564230799674988</v>
       </c>
       <c r="F5" t="n">
-        <v>22501162</v>
+        <v>22501168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08 21:30:00</t>
+          <t>2026-04-09 20:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5398016571998596</v>
+        <v>0.6835659146308899</v>
       </c>
       <c r="F6" t="n">
-        <v>22501161</v>
+        <v>22501169</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08 22:00:00</t>
+          <t>2026-04-09 22:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3676699697971344</v>
+        <v>0.3815212249755859</v>
       </c>
       <c r="F7" t="n">
-        <v>22501163</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-08 22:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.73008793592453</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501164</v>
+        <v>22501170</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,36 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -451,35 +463,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09 19:00:00</t>
+          <t>2026-04-10 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7684751152992249</v>
+        <v>0.5150246024131775</v>
       </c>
       <c r="F2" t="n">
-        <v>22501165</v>
+        <v>22501171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09 19:00:00</t>
+          <t>2026-04-10 19:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,86 +501,86 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2770043313503265</v>
+        <v>0.4738925993442535</v>
       </c>
       <c r="F3" t="n">
-        <v>22501166</v>
+        <v>22501172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09 19:30:00</t>
+          <t>2026-04-10 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4195958077907562</v>
+        <v>0.672922670841217</v>
       </c>
       <c r="F4" t="n">
-        <v>22501167</v>
+        <v>22501173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09 19:30:00</t>
+          <t>2026-04-10 19:30:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
       <c r="E5" t="n">
-        <v>0.3564230799674988</v>
+        <v>0.9048323035240173</v>
       </c>
       <c r="F5" t="n">
-        <v>22501168</v>
+        <v>22501174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09 20:00:00</t>
+          <t>2026-04-10 19:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,42 +590,294 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6835659146308899</v>
+        <v>0.535803496837616</v>
       </c>
       <c r="F6" t="n">
-        <v>22501169</v>
+        <v>22501175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09 22:00:00</t>
+          <t>2026-04-10 19:30:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5096167325973511</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22501176</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-10 20:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.111219123005867</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22501177</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-10 20:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7083379030227661</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22501179</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-10 20:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8614312410354614</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22501180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6415862441062927</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22501182</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:30:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6991291046142578</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22501178</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:30:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3756789565086365</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22501181</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-10 22:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6735097765922546</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22501183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-10 22:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4845962822437286</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22501184</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-10 22:30:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.3815212249755859</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22501170</v>
+      <c r="E16" t="n">
+        <v>0.5701608061790466</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22501185</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
@@ -463,421 +451,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-10 19:00:00</t>
+          <t>2025-10-02 12:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5150246024131775</v>
+        <v>0.6360629200935364</v>
       </c>
       <c r="F2" t="n">
-        <v>22501171</v>
+        <v>12500008</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-10 19:00:00</t>
+          <t>2025-10-03 22:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4738925993442535</v>
+        <v>0.4915966987609863</v>
       </c>
       <c r="F3" t="n">
-        <v>22501172</v>
+        <v>12500001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-10 19:00:00</t>
+          <t>2025-10-04 11:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.672922670841217</v>
+        <v>0.6432452797889709</v>
       </c>
       <c r="F4" t="n">
-        <v>22501173</v>
+        <v>12500010</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10 19:30:00</t>
+          <t>2025-10-04 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9048323035240173</v>
+        <v>0.5113423466682434</v>
       </c>
       <c r="F5" t="n">
-        <v>22501174</v>
+        <v>12500027</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-10 19:30:00</t>
+          <t>2025-10-04 21:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.535803496837616</v>
+        <v>0.8339630365371704</v>
       </c>
       <c r="F6" t="n">
-        <v>22501175</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-10 19:30:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5096167325973511</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22501176</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-10 20:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.111219123005867</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22501177</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-10 20:00:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.7083379030227661</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22501179</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-04-10 20:00:00</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8614312410354614</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22501180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04-10 21:00:00</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.6415862441062927</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22501182</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-04-10 21:30:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6991291046142578</v>
-      </c>
-      <c r="F12" t="n">
-        <v>22501178</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-04-10 21:30:00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.3756789565086365</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22501181</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-04-10 22:00:00</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.6735097765922546</v>
-      </c>
-      <c r="F14" t="n">
-        <v>22501183</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-04-10 22:00:00</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.4845962822437286</v>
-      </c>
-      <c r="F15" t="n">
-        <v>22501184</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-10 22:30:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.5701608061790466</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22501185</v>
+        <v>12500028</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,119 +451,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-02 12:00:00</t>
+          <t>2026-04-20 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6360629200935364</v>
+        <v>0.6051424145698547</v>
       </c>
       <c r="F2" t="n">
-        <v>12500008</v>
+        <v>42520001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-03 22:00:00</t>
+          <t>2026-04-20 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4915966987609863</v>
+        <v>0.5977880358695984</v>
       </c>
       <c r="F3" t="n">
-        <v>12500001</v>
+        <v>42520007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-04 11:00:00</t>
+          <t>2026-04-21 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6432452797889709</v>
+        <v>0.7210045456886292</v>
       </c>
       <c r="F4" t="n">
-        <v>12500010</v>
+        <v>42520013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-04 20:00:00</t>
+          <t>2026-04-21 20:00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5113423466682434</v>
+        <v>0.5657499432563782</v>
       </c>
       <c r="F5" t="n">
-        <v>12500027</v>
+        <v>42520031</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-04 21:00:00</t>
+          <t>2026-04-21 22:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -582,10 +582,94 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8339630365371704</v>
+        <v>0.7124065160751343</v>
       </c>
       <c r="F6" t="n">
-        <v>12500028</v>
+        <v>42520037</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:30:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6229561567306519</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42520043</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5598382949829102</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42520019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-22 21:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7073587775230408</v>
+      </c>
+      <c r="F9" t="n">
+        <v>42520025</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6051424145698547</v>
+        <v>0.6133015155792236</v>
       </c>
       <c r="F2" t="n">
         <v>42520001</v>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5977880358695984</v>
+        <v>0.584772527217865</v>
       </c>
       <c r="F3" t="n">
         <v>42520007</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7210045456886292</v>
+        <v>0.6660698056221008</v>
       </c>
       <c r="F4" t="n">
         <v>42520013</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5657499432563782</v>
+        <v>0.5945318937301636</v>
       </c>
       <c r="F5" t="n">
         <v>42520031</v>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7124065160751343</v>
+        <v>0.7690243721008301</v>
       </c>
       <c r="F6" t="n">
         <v>42520037</v>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6229561567306519</v>
+        <v>0.5765520930290222</v>
       </c>
       <c r="F7" t="n">
         <v>42520043</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5598382949829102</v>
+        <v>0.5548051595687866</v>
       </c>
       <c r="F8" t="n">
         <v>42520019</v>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7073587775230408</v>
+        <v>0.6796176433563232</v>
       </c>
       <c r="F9" t="n">
         <v>42520025</v>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,225 +451,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20 19:00:00</t>
+          <t>2026-04-23 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6133015155792236</v>
+        <v>0.4705749452114105</v>
       </c>
       <c r="F2" t="n">
-        <v>42520001</v>
+        <v>42520008</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20 20:00:00</t>
+          <t>2026-04-23 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.584772527217865</v>
+        <v>0.6515121459960938</v>
       </c>
       <c r="F3" t="n">
-        <v>42520007</v>
+        <v>42520002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21 19:00:00</t>
+          <t>2026-04-23 21:30:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6660698056221008</v>
+        <v>0.4369957447052002</v>
       </c>
       <c r="F4" t="n">
-        <v>42520013</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-04-21 20:00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.5945318937301636</v>
-      </c>
-      <c r="F5" t="n">
-        <v>42520031</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-21 22:30:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.7690243721008301</v>
-      </c>
-      <c r="F6" t="n">
-        <v>42520037</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-21 22:30:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5765520930290222</v>
-      </c>
-      <c r="F7" t="n">
-        <v>42520043</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-04-22 19:00:00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.5548051595687866</v>
-      </c>
-      <c r="F8" t="n">
-        <v>42520019</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-04-22 21:30:00</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6796176433563232</v>
-      </c>
-      <c r="F9" t="n">
-        <v>42520025</v>
+        <v>42520038</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -466,11 +466,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4705749452114105</v>
+        <v>0.5086182951927185</v>
       </c>
       <c r="F2" t="n">
         <v>42520008</v>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6515121459960938</v>
+        <v>0.6422564387321472</v>
       </c>
       <c r="F3" t="n">
         <v>42520002</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4369957447052002</v>
+        <v>0.4874036014080048</v>
       </c>
       <c r="F4" t="n">
         <v>42520038</v>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -451,85 +451,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23 19:00:00</t>
+          <t>2026-04-24 19:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5086182951927185</v>
+        <v>0.4534924924373627</v>
       </c>
       <c r="F2" t="n">
-        <v>42520008</v>
+        <v>42520014</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23 20:00:00</t>
+          <t>2026-04-24 20:00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6422564387321472</v>
+        <v>0.6931077837944031</v>
       </c>
       <c r="F3" t="n">
-        <v>42520002</v>
+        <v>42520044</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23 21:30:00</t>
+          <t>2026-04-24 22:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4874036014080048</v>
+        <v>0.511742115020752</v>
       </c>
       <c r="F4" t="n">
-        <v>42520038</v>
+        <v>42520032</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,85 +451,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-24 19:00:00</t>
+          <t>2026-04-26 13:00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4534924924373627</v>
+        <v>0.5131328105926514</v>
       </c>
       <c r="F2" t="n">
-        <v>42520014</v>
+        <v>42500134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-24 20:00:00</t>
+          <t>2026-04-26 15:30:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6931077837944031</v>
+        <v>0.3003147840499878</v>
       </c>
       <c r="F3" t="n">
-        <v>42520044</v>
+        <v>42500154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-24 22:00:00</t>
+          <t>2026-04-26 19:00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.511742115020752</v>
+        <v>0.3551293909549713</v>
       </c>
       <c r="F4" t="n">
-        <v>42520032</v>
+        <v>42500114</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-26 21:30:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5205807685852051</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42500174</v>
       </c>
     </row>
   </sheetData>

--- a/output/predictions.xlsx
+++ b/output/predictions.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>market_prob_home_win</t>
         </is>
@@ -456,32 +468,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-17 20:00:00</t>
+          <t>2026-05-20 20:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6623931623931624</v>
       </c>
       <c r="F2" t="n">
-        <v>42500207</v>
+        <v>42500312</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6279</v>
+        <v>0.6843</v>
       </c>
     </row>
   </sheetData>
